--- a/r5-TC-FHIR-AG-Scheduling-R5-interation-documentation/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-interation-documentation/StructureDefinition-at-scheduling-appointment.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5568" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5568" uniqueCount="610">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T16:14:22+00:00</t>
+    <t>2025-03-08T14:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1443,9 +1443,6 @@
   </si>
   <si>
     <t>Appointment.participant:HL7ATCorePatient.actor.display</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
   </si>
   <si>
     <t>Appointment.participant:HL7ATCorePatient.required</t>
@@ -9869,7 +9866,7 @@
         <v>87</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>18</v>
@@ -9887,7 +9884,7 @@
         <v>417</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>449</v>
+        <v>202</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9969,7 +9966,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>419</v>
@@ -10086,7 +10083,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>426</v>
@@ -10103,7 +10100,7 @@
         <v>87</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>18</v>
@@ -10201,13 +10198,13 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>347</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>18</v>
@@ -10318,7 +10315,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>358</v>
@@ -10433,7 +10430,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>363</v>
@@ -10550,7 +10547,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>366</v>
@@ -10669,7 +10666,7 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>371</v>
@@ -10786,7 +10783,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>380</v>
@@ -10901,7 +10898,7 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>383</v>
@@ -10927,7 +10924,7 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L75" t="s" s="2">
         <v>385</v>
@@ -11018,7 +11015,7 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>391</v>
@@ -11133,7 +11130,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>392</v>
@@ -11250,7 +11247,7 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>395</v>
@@ -11367,7 +11364,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>401</v>
@@ -11484,7 +11481,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>408</v>
@@ -11601,7 +11598,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>415</v>
@@ -11618,7 +11615,7 @@
         <v>87</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>18</v>
@@ -11636,7 +11633,7 @@
         <v>417</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>449</v>
+        <v>202</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11718,7 +11715,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>419</v>
@@ -11835,7 +11832,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>426</v>
@@ -11852,7 +11849,7 @@
         <v>87</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>18</v>
@@ -11950,13 +11947,13 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>347</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>18</v>
@@ -12067,7 +12064,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>358</v>
@@ -12182,7 +12179,7 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>363</v>
@@ -12299,7 +12296,7 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>366</v>
@@ -12418,7 +12415,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>371</v>
@@ -12535,7 +12532,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>380</v>
@@ -12650,7 +12647,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>383</v>
@@ -12676,7 +12673,7 @@
         <v>88</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>385</v>
@@ -12767,7 +12764,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>391</v>
@@ -12882,7 +12879,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>392</v>
@@ -12999,7 +12996,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>395</v>
@@ -13116,7 +13113,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>401</v>
@@ -13233,7 +13230,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>408</v>
@@ -13350,7 +13347,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>415</v>
@@ -13367,7 +13364,7 @@
         <v>87</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>18</v>
@@ -13385,7 +13382,7 @@
         <v>417</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>449</v>
+        <v>202</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13467,7 +13464,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>419</v>
@@ -13584,7 +13581,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>426</v>
@@ -13601,7 +13598,7 @@
         <v>87</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>18</v>
@@ -13699,13 +13696,13 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>347</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>18</v>
@@ -13816,7 +13813,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>358</v>
@@ -13931,7 +13928,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>363</v>
@@ -14048,7 +14045,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>366</v>
@@ -14167,7 +14164,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>371</v>
@@ -14284,7 +14281,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>380</v>
@@ -14399,7 +14396,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>383</v>
@@ -14425,7 +14422,7 @@
         <v>88</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="L105" t="s" s="2">
         <v>385</v>
@@ -14516,7 +14513,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>391</v>
@@ -14631,7 +14628,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>392</v>
@@ -14748,7 +14745,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>395</v>
@@ -14865,7 +14862,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>401</v>
@@ -14982,7 +14979,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>408</v>
@@ -15099,7 +15096,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>415</v>
@@ -15216,7 +15213,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>419</v>
@@ -15333,7 +15330,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>426</v>
@@ -15448,10 +15445,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15477,10 +15474,10 @@
         <v>284</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15531,7 +15528,7 @@
         <v>18</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -15563,10 +15560,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15592,13 +15589,13 @@
         <v>420</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -15648,7 +15645,7 @@
         <v>18</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -15680,10 +15677,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15709,10 +15706,10 @@
         <v>348</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15763,7 +15760,7 @@
         <v>18</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
@@ -15795,10 +15792,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15910,10 +15907,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16027,10 +16024,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16146,10 +16143,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16175,10 +16172,10 @@
         <v>168</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16208,11 +16205,11 @@
         <v>111</v>
       </c>
       <c r="Y120" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="Z120" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="Z120" t="s" s="2">
-        <v>520</v>
-      </c>
       <c r="AA120" t="s" s="2">
         <v>18</v>
       </c>
@@ -16229,7 +16226,7 @@
         <v>18</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
@@ -16253,7 +16250,7 @@
         <v>132</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>18</v>
@@ -16261,10 +16258,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16290,10 +16287,10 @@
         <v>168</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16323,10 +16320,10 @@
         <v>178</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>18</v>
@@ -16344,7 +16341,7 @@
         <v>18</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>87</v>
@@ -16368,7 +16365,7 @@
         <v>18</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>18</v>
@@ -16376,10 +16373,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16402,13 +16399,13 @@
         <v>18</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L122" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="L122" t="s" s="2">
+      <c r="M122" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16459,7 +16456,7 @@
         <v>18</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -16483,7 +16480,7 @@
         <v>18</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>18</v>
@@ -16491,10 +16488,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16520,10 +16517,10 @@
         <v>284</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16574,7 +16571,7 @@
         <v>18</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
@@ -16598,7 +16595,7 @@
         <v>18</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>18</v>
@@ -16606,10 +16603,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16632,13 +16629,13 @@
         <v>18</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16689,7 +16686,7 @@
         <v>18</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -16713,7 +16710,7 @@
         <v>18</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>18</v>
@@ -16721,10 +16718,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16750,10 +16747,10 @@
         <v>348</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -16804,7 +16801,7 @@
         <v>18</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -16836,10 +16833,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16951,10 +16948,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17068,10 +17065,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17187,10 +17184,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17216,10 +17213,10 @@
         <v>420</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17270,7 +17267,7 @@
         <v>18</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
@@ -17302,10 +17299,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17331,10 +17328,10 @@
         <v>420</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -17385,7 +17382,7 @@
         <v>18</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
@@ -17417,10 +17414,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17446,10 +17443,10 @@
         <v>420</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17500,7 +17497,7 @@
         <v>18</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -17532,10 +17529,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17561,10 +17558,10 @@
         <v>420</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -17615,7 +17612,7 @@
         <v>18</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -17647,10 +17644,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17676,10 +17673,10 @@
         <v>420</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -17730,7 +17727,7 @@
         <v>18</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -17762,10 +17759,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17791,10 +17788,10 @@
         <v>420</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -17845,7 +17842,7 @@
         <v>18</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -17877,10 +17874,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17906,10 +17903,10 @@
         <v>420</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -17960,7 +17957,7 @@
         <v>18</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>76</v>
@@ -17992,10 +17989,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18021,10 +18018,10 @@
         <v>284</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18075,7 +18072,7 @@
         <v>18</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>76</v>
@@ -18107,10 +18104,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18136,10 +18133,10 @@
         <v>348</v>
       </c>
       <c r="L137" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M137" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -18190,7 +18187,7 @@
         <v>18</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>76</v>
@@ -18222,10 +18219,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18337,10 +18334,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18454,10 +18451,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18573,10 +18570,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18602,10 +18599,10 @@
         <v>284</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -18656,7 +18653,7 @@
         <v>18</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
@@ -18688,10 +18685,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18714,13 +18711,13 @@
         <v>18</v>
       </c>
       <c r="K142" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="L142" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="L142" t="s" s="2">
+      <c r="M142" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -18750,11 +18747,11 @@
         <v>111</v>
       </c>
       <c r="Y142" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="Z142" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="Z142" t="s" s="2">
-        <v>584</v>
-      </c>
       <c r="AA142" t="s" s="2">
         <v>18</v>
       </c>
@@ -18771,7 +18768,7 @@
         <v>18</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>76</v>
@@ -18803,10 +18800,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18829,16 +18826,16 @@
         <v>18</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="N143" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -18867,11 +18864,11 @@
         <v>111</v>
       </c>
       <c r="Y143" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="Z143" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="Z143" t="s" s="2">
-        <v>590</v>
-      </c>
       <c r="AA143" t="s" s="2">
         <v>18</v>
       </c>
@@ -18888,7 +18885,7 @@
         <v>18</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>76</v>
@@ -18920,10 +18917,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18949,10 +18946,10 @@
         <v>284</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -19003,7 +19000,7 @@
         <v>18</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>87</v>
@@ -19035,10 +19032,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19064,10 +19061,10 @@
         <v>348</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -19118,7 +19115,7 @@
         <v>18</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>76</v>
@@ -19150,10 +19147,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19265,10 +19262,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19382,10 +19379,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19501,10 +19498,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19530,10 +19527,10 @@
         <v>284</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -19584,7 +19581,7 @@
         <v>18</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>87</v>
@@ -19616,10 +19613,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19642,16 +19639,16 @@
         <v>18</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="N150" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -19701,7 +19698,7 @@
         <v>18</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>76</v>
@@ -19725,7 +19722,7 @@
         <v>18</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>18</v>
@@ -19733,10 +19730,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19762,13 +19759,13 @@
         <v>284</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="N151" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -19818,7 +19815,7 @@
         <v>18</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>76</v>

--- a/r5-TC-FHIR-AG-Scheduling-R5-interation-documentation/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-interation-documentation/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-08T14:41:39+00:00</t>
+    <t>2025-03-08T14:51:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
